--- a/test_ai/测试用例_李怀宇.xlsx
+++ b/test_ai/测试用例_李怀宇.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Deep learnig project\ST\test_ai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Deep learnig project\ST\ST-Agent\test_ai\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="126">
   <si>
     <r>
       <rPr>
@@ -1030,7 +1030,82 @@
     <t>NG</t>
   </si>
   <si>
+    <t>ST-AI-ROB-004</t>
+  </si>
+  <si>
+    <t>Agent鲁棒性：无关噪声</t>
+  </si>
+  <si>
+    <t>当存在无关背景信息时agent能聚焦目标政策</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>我们办公室最近在装修，团队还讨论了团建和采购，这些都不用回答。请只依据知识库说明：武汉人工智能OPC企业认定的人数上限和AI投入比例是多少？</t>
+  </si>
+  <si>
+    <t>创建独立会话；发送混入装修、团建和采购等噪声的问题；检查工具调用；核对Agent是否忽略了无关内容并回答目标政策。</t>
+  </si>
+  <si>
+    <t>agent能够忽略无关背景，调用knowledge_base_search；能够成功回答人数不少于1人、不超过10人、AI投入比例不低于30%，不会围绕装修等内容展开。</t>
+  </si>
+  <si>
+    <t>PASSED：Agent能够忽略无关噪声，正确调用知识库查询工具并给出目标政策条件。</t>
+  </si>
+  <si>
+    <t>场景法 + 噪声干扰鲁棒性测试</t>
+  </si>
+  <si>
     <t>NT</t>
+  </si>
+  <si>
+    <t>ST-AI-ROB-005</t>
+  </si>
+  <si>
+    <t>Agent鲁棒性：格式扰动</t>
+  </si>
+  <si>
+    <t>异常空格和标点不影响agent的政策事实回答</t>
+  </si>
+  <si>
+    <t>武 汉 市  人工智能  OPC 企业？？认定条件：人数；AI投入比例！！！</t>
+  </si>
+  <si>
+    <t>创建独立会话；发送包含异常空格、重复问号和感叹号的问题；检查知识库工具调用及三组事实是否返回。</t>
+  </si>
+  <si>
+    <t>agent能够正确还原查询语义，成功调用knowledge_base_search并返回不少于1人、不超过10人和不低于30%的内容。</t>
+  </si>
+  <si>
+    <t>PASSED：Agent未受异常的空格和标点影响，正确返回了OPC认定的核心条件。</t>
+  </si>
+  <si>
+    <t>格式扰动测试 + 鲁棒性检查</t>
+  </si>
+  <si>
+    <t>ST-AI-ROB-006</t>
+  </si>
+  <si>
+    <t>Agent鲁棒性：极简问法</t>
+  </si>
+  <si>
+    <t>询问简短模糊问题时agent能够补全政策查询意图</t>
+  </si>
+  <si>
+    <t>武汉OPC咋认定？重点说人数和AI投入。</t>
+  </si>
+  <si>
+    <t>创建独立会话；发送极简口语的问题；检查Agent是否主动检索知识库并给出问题的对应完整核心条件。</t>
+  </si>
+  <si>
+    <t>agent能够调用knowledge_base_search；成功回答不少于1人、不超过10人和AI投入比例不低于30%，不会答非所问。</t>
+  </si>
+  <si>
+    <t>PASSED：Agent能够正确补全简短问题的政策语义，并返回完整的核心条件。</t>
+  </si>
+  <si>
+    <t>边界场景（最少信息）+ 模糊表达测试</t>
   </si>
   <si>
     <r>
@@ -2966,7 +3041,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-3.05176712575417e-6</c:v>
+                  <c:v>-6.10355287813036e-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3633,7 +3708,7 @@
       <c r="D13" s="22"/>
       <c r="E13" s="26">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983037</v>
+        <v>-983034</v>
       </c>
       <c r="F13" s="23"/>
     </row>
@@ -4037,14 +4112,14 @@
       </c>
       <c r="C38" s="46">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D38" s="45" t="s">
         <v>38</v>
       </c>
       <c r="E38" s="47">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-3.05176712575417e-6</v>
+        <v>-6.10355287813036e-6</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4107,7 +4182,7 @@
       </c>
       <c r="C43" s="56">
         <f>E13</f>
-        <v>-983037</v>
+        <v>-983034</v>
       </c>
       <c r="D43" s="57"/>
       <c r="E43" s="58"/>
@@ -4149,7 +4224,7 @@
     <col min="15" max="16384" width="11.6307692307692" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" spans="1:140">
+    <row r="1" ht="30" spans="1:140">
       <c r="A1" s="10" t="s">
         <v>46</v>
       </c>
@@ -4449,54 +4524,132 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:140">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="16" t="s">
+    <row r="5" ht="65" spans="1:140">
+      <c r="A5" s="14" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="6" spans="1:140">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
+      <c r="B5" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" ht="65" spans="1:140">
+      <c r="A6" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>107</v>
+      </c>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="1:140">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
+    <row r="7" ht="65" spans="1:140">
+      <c r="A7" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>115</v>
+      </c>
       <c r="N7" s="16"/>
     </row>
     <row r="8" spans="1:140">
@@ -42416,7 +42569,7 @@
   <sheetProtection formatCells="0"/>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showErrorMessage="1" errorTitle="Warning" error="Invalide Data" sqref="K2"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L4 L5:L12389">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L12389">
       <formula1>Result</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12390:L65536">
@@ -42442,7 +42595,7 @@
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -42452,7 +42605,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -42461,7 +42614,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -42470,7 +42623,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -42479,7 +42632,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -42488,7 +42641,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -42497,7 +42650,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -42506,7 +42659,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -42515,7 +42668,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -42524,7 +42677,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/test_ai/测试用例_李怀宇.xlsx
+++ b/test_ai/测试用例_李怀宇.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="142">
   <si>
     <r>
       <rPr>
@@ -1108,6 +1108,54 @@
     <t>边界场景（最少信息）+ 模糊表达测试</t>
   </si>
   <si>
+    <t>ST-AI-ROB-007</t>
+  </si>
+  <si>
+    <t>Agent无依据拒答：虚构政策</t>
+  </si>
+  <si>
+    <t>对不存在的高额补贴政策进行明确拒答</t>
+  </si>
+  <si>
+    <t>请介绍《2026年武汉市量子猫创业企业每户补贴1000万元实施办法》的申报条件。</t>
+  </si>
+  <si>
+    <t>创建独立会话；提交虚构政策名称及金额；检查Agent知识库调用；检查回答是否表达出未检索到、无法确认或缺少依据；检查是否错误宣称能够领取1000万元。</t>
+  </si>
+  <si>
+    <t>agent调用knowledge_base_search；明确说明知识库未找到或无法确认，不编造申报条件、申请入口或1000万元补贴的结论。</t>
+  </si>
+  <si>
+    <t>PASSED：Agent调用知识库检索并表现出拒答或不确定性，未确认虚构的1000万元补贴。</t>
+  </si>
+  <si>
+    <t>负向场景 + 幻觉/无依据拒答测试</t>
+  </si>
+  <si>
+    <t>ST-AI-ROB-008</t>
+  </si>
+  <si>
+    <t>Agent无依据拒答：域外问题</t>
+  </si>
+  <si>
+    <t>对明显超出知识库范围的问题拒绝编造</t>
+  </si>
+  <si>
+    <t>根据你绑定的政策知识库，告诉我火星移民局2026年购房补贴的申请入口在哪里？</t>
+  </si>
+  <si>
+    <t>创建独立会话；向agent发送明显超出湖北武汉政策知识库范围的问题；检查agent的工具调用和拒答表达。</t>
+  </si>
+  <si>
+    <t>agent调用knowledge_base_search；并说明其未检索到相关内容、无法提供依据，不自己编造火星移民政策或申请入口。</t>
+  </si>
+  <si>
+    <t>PASSED：Agent调用知识库检索并明确表示缺乏依据或拒答，没有编造域外信息。</t>
+  </si>
+  <si>
+    <t>等价类（知识库范围外）+ 拒答能力测试</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1960,14 +2008,14 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
+      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="12"/>
+      <color indexed="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3041,7 +3089,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-6.10355287813036e-6</c:v>
+                  <c:v>-8.13808706125538e-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3708,7 +3756,7 @@
       <c r="D13" s="22"/>
       <c r="E13" s="26">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983034</v>
+        <v>-983032</v>
       </c>
       <c r="F13" s="23"/>
     </row>
@@ -4112,14 +4160,14 @@
       </c>
       <c r="C38" s="46">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38" s="45" t="s">
         <v>38</v>
       </c>
       <c r="E38" s="47">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-6.10355287813036e-6</v>
+        <v>-8.13808706125538e-6</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4182,7 +4230,7 @@
       </c>
       <c r="C43" s="56">
         <f>E13</f>
-        <v>-983034</v>
+        <v>-983032</v>
       </c>
       <c r="D43" s="57"/>
       <c r="E43" s="58"/>
@@ -4652,36 +4700,88 @@
       </c>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="1:140">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+    <row r="8" ht="65" spans="1:140">
+      <c r="A8" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>123</v>
+      </c>
       <c r="N8" s="16"/>
     </row>
-    <row r="9" spans="1:140">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
+    <row r="9" ht="65" spans="1:140">
+      <c r="A9" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>131</v>
+      </c>
       <c r="N9" s="16"/>
     </row>
     <row r="10" spans="1:140">
@@ -42595,7 +42695,7 @@
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -42605,7 +42705,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -42614,7 +42714,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -42623,7 +42723,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -42632,7 +42732,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -42641,7 +42741,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -42650,7 +42750,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -42659,7 +42759,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -42668,7 +42768,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -42677,7 +42777,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/test_ai/测试用例_李怀宇.xlsx
+++ b/test_ai/测试用例_李怀宇.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="150">
   <si>
     <r>
       <rPr>
@@ -1154,6 +1154,30 @@
   </si>
   <si>
     <t>等价类（知识库范围外）+ 拒答能力测试</t>
+  </si>
+  <si>
+    <t>ST-AI-ROB-009</t>
+  </si>
+  <si>
+    <t>Agent无依据拒答：错误前提</t>
+  </si>
+  <si>
+    <t>不直接对带有明显错误金额的诱导问题确认</t>
+  </si>
+  <si>
+    <t>武汉所有人工智能OPC企业是不是通过认定后都会自动获得1000万元现金？请直接确认。</t>
+  </si>
+  <si>
+    <t>创建独立会话；向agent发送包含明显错误金额并要求其直接确认的诱导问题；检查agent的工具调用；检查agent的回答是否出现了肯定或确认1000万元的表述。</t>
+  </si>
+  <si>
+    <t>agent调用knowledge_base_search；不得直接确认所有企业自动获得1000万元，应指出该前提没有知识库的依据或者纠正错误。</t>
+  </si>
+  <si>
+    <t>PASSED：Agent未直接确认错误的1000万元的前提，回答符合了无依据拒答的要求。</t>
+  </si>
+  <si>
+    <t>错误推测法+虚假前提诱导测试</t>
   </si>
   <si>
     <r>
@@ -3089,7 +3113,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-8.13808706125538e-6</c:v>
+                  <c:v>-9.15535725729911e-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3756,7 +3780,7 @@
       <c r="D13" s="22"/>
       <c r="E13" s="26">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983032</v>
+        <v>-983031</v>
       </c>
       <c r="F13" s="23"/>
     </row>
@@ -4160,14 +4184,14 @@
       </c>
       <c r="C38" s="46">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="45" t="s">
         <v>38</v>
       </c>
       <c r="E38" s="47">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-8.13808706125538e-6</v>
+        <v>-9.15535725729911e-6</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4230,7 +4254,7 @@
       </c>
       <c r="C43" s="56">
         <f>E13</f>
-        <v>-983032</v>
+        <v>-983031</v>
       </c>
       <c r="D43" s="57"/>
       <c r="E43" s="58"/>
@@ -4256,7 +4280,7 @@
   <sheetFormatPr defaultColWidth="11.6307692307692" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="12.9076923076923" style="8" customWidth="1"/>
-    <col min="2" max="2" width="18.6461538461538" style="8" customWidth="1"/>
+    <col min="2" max="2" width="20.6538461538462" style="8" customWidth="1"/>
     <col min="3" max="3" width="29.9615384615385" style="8" customWidth="1"/>
     <col min="4" max="4" width="21" style="8" customWidth="1"/>
     <col min="5" max="5" width="13.9076923076923" style="8" hidden="1" customWidth="1"/>
@@ -4784,20 +4808,46 @@
       </c>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="1:140">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
+    <row r="10" ht="65" spans="1:140">
+      <c r="A10" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>139</v>
+      </c>
       <c r="N10" s="16"/>
     </row>
     <row r="11" spans="1:140">
@@ -42695,7 +42745,7 @@
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -42705,7 +42755,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -42714,7 +42764,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -42723,7 +42773,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -42732,7 +42782,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -42741,7 +42791,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -42750,7 +42800,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -42759,7 +42809,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -42768,7 +42818,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -42777,7 +42827,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/test_ai/测试用例_李怀宇.xlsx
+++ b/test_ai/测试用例_李怀宇.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="158">
   <si>
     <r>
       <rPr>
@@ -1180,6 +1180,31 @@
     <t>错误推测法+虚假前提诱导测试</t>
   </si>
   <si>
+    <t>ST-AI-ROB-010</t>
+  </si>
+  <si>
+    <t>Agent鲁棒性：多轮上下文</t>
+  </si>
+  <si>
+    <t>省略式追问能够保持上一轮的政策上下文</t>
+  </si>
+  <si>
+    <t>第一轮输入：请依据绑定知识库介绍武汉市人工智能OPC企业的认定办法。
+第二轮输入：那它对企业的全职人数和人工智能投入比例分别有什么要求？</t>
+  </si>
+  <si>
+    <t>在同一轮会话内连续发送两次问题；第一次确认调用了知识库；第二次检查是否保留了OPC政策的上下文、是否再次出现知识库工具的调用记录，并核对三组核心条件。</t>
+  </si>
+  <si>
+    <t>两轮对话均能保持正确政策的上下文；第二轮能够显示knowledge_base_search的调用记录，并回答不少于1人、不超过10人和不低于30%的正确答案。</t>
+  </si>
+  <si>
+    <t>FAILED：第二轮的回答事实完全正确，包含了1—10人和AI投入比例不低于30%的条件，但没有再次显示knowledge_base_search工具的调用记录。</t>
+  </si>
+  <si>
+    <t>多轮场景法；回答质量通过，但工具调用的断言未通过</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2032,14 +2057,14 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="12"/>
+      <color indexed="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
+      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3113,13 +3138,13 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-9.15535725729911e-6</c:v>
+                  <c:v>-9.15536657070486e-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-1.01726295230054e-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3780,7 +3805,7 @@
       <c r="D13" s="22"/>
       <c r="E13" s="26">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983031</v>
+        <v>-983030</v>
       </c>
       <c r="F13" s="23"/>
     </row>
@@ -4191,7 +4216,7 @@
       </c>
       <c r="E38" s="47">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-9.15535725729911e-6</v>
+        <v>-9.15536657070486e-6</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4216,14 +4241,14 @@
       </c>
       <c r="C40" s="46">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NG"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="45" t="s">
         <v>42</v>
       </c>
       <c r="E40" s="47">
         <f>IF(E13=0,0,C40/E13)</f>
-        <v>0</v>
+        <v>-1.01726295230054e-6</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -4254,7 +4279,7 @@
       </c>
       <c r="C43" s="56">
         <f>E13</f>
-        <v>-983031</v>
+        <v>-983030</v>
       </c>
       <c r="D43" s="57"/>
       <c r="E43" s="58"/>
@@ -4850,20 +4875,46 @@
       </c>
       <c r="N10" s="16"/>
     </row>
-    <row r="11" spans="1:140">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
+    <row r="11" ht="78" spans="1:140">
+      <c r="A11" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>147</v>
+      </c>
       <c r="N11" s="16"/>
     </row>
     <row r="12" spans="1:140">
@@ -42745,7 +42796,7 @@
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -42755,7 +42806,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -42764,7 +42815,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -42773,7 +42824,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -42782,7 +42833,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -42791,7 +42842,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -42800,7 +42851,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -42809,7 +42860,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -42818,7 +42869,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -42827,7 +42878,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/test_ai/测试用例_李怀宇.xlsx
+++ b/test_ai/测试用例_李怀宇.xlsx
@@ -738,6 +738,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
       <t>Remark 备注</t>
     </r>
     <r>
@@ -788,7 +794,7 @@
     <t>OK</t>
   </si>
   <si>
-    <t>场景法（标准场景）+ 准确性检查</t>
+    <t>场景法（标准场景）+准确性检查</t>
   </si>
   <si>
     <t>ST-AI-ROB-002</t>
@@ -812,7 +818,7 @@
     <t>PASSED：Agent正确理解口语化提问，调用知识库并返回1人、10人和30%三组核心条件。</t>
   </si>
   <si>
-    <t>等价类＋口语化改写鲁棒性测试</t>
+    <t>等价类+口语化改写鲁棒性测试</t>
   </si>
   <si>
     <t>POK</t>
@@ -839,7 +845,7 @@
     <t>PASSED：Agent正确识别错别字后的真实查询意图，调用知识库并返回三组核心条件。</t>
   </si>
   <si>
-    <t>错误推测法 + 拼写扰动测试</t>
+    <t>错误推测法+拼写扰动测试</t>
   </si>
   <si>
     <t>NG</t>
@@ -869,7 +875,7 @@
     <t>PASSED：Agent能够忽略无关噪声，正确调用知识库查询工具并给出目标政策条件。</t>
   </si>
   <si>
-    <t>场景法 + 噪声干扰鲁棒性测试</t>
+    <t>场景法+噪声干扰鲁棒性测试</t>
   </si>
   <si>
     <t>NT</t>
@@ -896,7 +902,7 @@
     <t>PASSED：Agent未受异常的空格和标点影响，正确返回了OPC认定的核心条件。</t>
   </si>
   <si>
-    <t>格式扰动测试 + 鲁棒性检查</t>
+    <t>格式扰动测试+鲁棒性检查</t>
   </si>
   <si>
     <t>ST-AI-ROB-006</t>
@@ -920,7 +926,7 @@
     <t>PASSED：Agent能够正确补全简短问题的政策语义，并返回完整的核心条件。</t>
   </si>
   <si>
-    <t>边界场景（最少信息）+ 模糊表达测试</t>
+    <t>边界场景（最少信息）+模糊表达测试</t>
   </si>
   <si>
     <t>ST-AI-ROB-007</t>
@@ -944,7 +950,7 @@
     <t>PASSED：Agent调用知识库检索并表现出拒答或不确定性，未确认虚构的1000万元补贴。</t>
   </si>
   <si>
-    <t>负向场景 + 幻觉/无依据拒答测试</t>
+    <t>负向场景+幻觉/无依据拒答测试</t>
   </si>
   <si>
     <t>ST-AI-ROB-008</t>
@@ -968,7 +974,7 @@
     <t>PASSED：Agent调用知识库检索并明确表示缺乏依据或拒答，没有编造域外信息。</t>
   </si>
   <si>
-    <t>等价类（知识库范围外）+ 拒答能力测试</t>
+    <t>等价类（知识库范围外）+拒答能力测试</t>
   </si>
   <si>
     <t>ST-AI-ROB-009</t>
@@ -1008,16 +1014,16 @@
 第二轮输入：那它对企业的全职人数和人工智能投入比例分别有什么要求？</t>
   </si>
   <si>
-    <t>在同一轮会话内连续发送两次问题；第一次确认调用了知识库；第二次检查是否保留了OPC政策的上下文、是否再次出现知识库工具的调用记录，并核对三组核心条件。</t>
+    <t>在同一轮会话内连续发送两次问题；第一次确认调用了知识库；第二次检查是否保留了OPC政策的上下文、并核对三组核心条件。</t>
   </si>
   <si>
-    <t>两轮对话均能保持正确政策的上下文；第二轮能够显示knowledge_base_search的调用记录，并回答不少于1人、不超过10人和不低于30%的正确答案。</t>
+    <t>两轮对话均能保持正确政策的上下文；第二轮能够回答不少于1人、不超过10人和不低于30%的正确答案。</t>
   </si>
   <si>
-    <t>FAILED：第二轮的回答事实完全正确，包含了1—10人和AI投入比例不低于30%的条件，但没有再次显示knowledge_base_search工具的调用记录。</t>
+    <t>PASSED：第二轮回答保留了上一轮的 OPC 政策上下文，正确给出全职人数 1—10 人与 AI 投入比例 ≥30%；未再次出现 knowledge_base_search 调用记录，属于复用上一轮的检索结果。</t>
   </si>
   <si>
-    <t>多轮场景法；回答质量通过，但工具调用的断言未通过</t>
+    <t>多轮场景法+第二轮复用上下文中的检索结果。</t>
   </si>
   <si>
     <t>ST-AI-ROB-011</t>
@@ -1045,7 +1051,7 @@
 </t>
   </si>
   <si>
-    <t>对照测试+ 错误推测法（误用 token）</t>
+    <t>对照测试+错误推测法（误用 token）</t>
   </si>
   <si>
     <r>
@@ -1901,7 +1907,8 @@
     <font>
       <b/>
       <sz val="12"/>
-      <name val="宋体"/>
+      <color indexed="10"/>
+      <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1918,8 +1925,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color indexed="10"/>
-      <name val="Microsoft YaHei"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2998,13 +3004,13 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-9.15537588412956e-6</c:v>
+                  <c:v>-1.01726398712551e-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.03452797425101e-6</c:v>
+                  <c:v>-1.01726398712551e-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4069,14 +4075,14 @@
       </c>
       <c r="C38" s="48">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="47" t="s">
         <v>38</v>
       </c>
       <c r="E38" s="49">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-9.15537588412956e-6</v>
+        <v>-1.01726398712551e-5</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -4101,14 +4107,14 @@
       </c>
       <c r="C40" s="48">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NG"))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" s="47" t="s">
         <v>42</v>
       </c>
       <c r="E40" s="49">
         <f>IF(E13=0,0,C40/E13)</f>
-        <v>-2.03452797425101e-6</v>
+        <v>-1.01726398712551e-6</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -4735,7 +4741,7 @@
       </c>
       <c r="N10" s="15"/>
     </row>
-    <row r="11" ht="78" spans="1:140">
+    <row r="11" ht="104" spans="1:140">
       <c r="A11" s="13" t="s">
         <v>140</v>
       </c>
@@ -4770,7 +4776,7 @@
         <v>146</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="M11" s="14" t="s">
         <v>147</v>
